--- a/d/2026-08-03_会员有效性分析.xlsx
+++ b/d/2026-08-03_会员有效性分析.xlsx
@@ -13,6 +13,7 @@
     <sheet name="门店无效号码明细" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="异常会员号码(跨门店高频)" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="异常明细(订单级)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="内部业务礼品单" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -532,19 +533,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>979</v>
+        <v>927</v>
       </c>
       <c r="C5" t="n">
-        <v>931</v>
+        <v>890</v>
       </c>
       <c r="D5" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="E5" t="n">
-        <v>95.09999999999999</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>4.9</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="6">
@@ -554,19 +555,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="C6" t="n">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>95.68000000000001</v>
+        <v>96.58</v>
       </c>
       <c r="F6" t="n">
-        <v>4.32</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="7">
@@ -1251,16 +1252,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F24" t="n">
         <v>7</v>
       </c>
       <c r="G24" t="n">
-        <v>23.33</v>
+        <v>24.14</v>
       </c>
     </row>
     <row r="25">
@@ -1323,25 +1324,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>华为北京昌平政府街</t>
+          <t>APR成都凯德魅力城</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
         <v>6</v>
       </c>
       <c r="G27" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28">
@@ -1350,7 +1351,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>APR成都凯德魅力城</t>
+          <t>APR成都高新伊藤</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1359,16 +1360,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>75</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="29">
@@ -1377,25 +1378,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>APR成都高新伊藤</t>
+          <t>DJI北京朝阳大悦城授权体验店</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E29" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F29" t="n">
         <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>15.15</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="30">
@@ -1404,25 +1405,25 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DJI北京朝阳大悦城授权体验店</t>
+          <t>APR成都金楠天街</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="F30" t="n">
         <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>16.13</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="31">
@@ -1431,7 +1432,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>APR成都金楠天街</t>
+          <t>APR成都温江伊藤</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1440,16 +1441,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E31" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>41.67</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="32">
@@ -1458,12 +1459,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>APR成都温江伊藤</t>
+          <t>DJI上海静安大融城授权体验店</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1485,25 +1486,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DJI上海静安大融城授权体验店</t>
+          <t>DJI北京丽泽天街授权体验店</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="E33" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="F33" t="n">
         <v>4</v>
       </c>
       <c r="G33" t="n">
-        <v>26.67</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="34">
@@ -1512,25 +1513,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DJI北京丽泽天街授权体验店</t>
+          <t>DJI上海凯德晶萃授权体验店</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="E34" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="F34" t="n">
         <v>4</v>
       </c>
       <c r="G34" t="n">
-        <v>8.33</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="35">
@@ -1539,7 +1540,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DJI上海凯德晶萃授权体验店</t>
+          <t>DJI上海复地活力城授权体验店</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1548,16 +1549,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E35" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F35" t="n">
         <v>4</v>
       </c>
       <c r="G35" t="n">
-        <v>21.05</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="36">
@@ -1566,25 +1567,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DJI上海复地活力城授权体验店</t>
+          <t>APR成都西宸天街</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E36" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F36" t="n">
         <v>4</v>
       </c>
       <c r="G36" t="n">
-        <v>22.22</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="37">
@@ -1593,25 +1594,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>APR成都西宸天街</t>
+          <t>DJI北京太阳宫凯德授权体验店</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E37" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F37" t="n">
         <v>4</v>
       </c>
       <c r="G37" t="n">
-        <v>16.67</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="38">
@@ -1620,25 +1621,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DJI北京太阳宫凯德授权体验店</t>
+          <t>华为北京京投小站</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E38" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
         <v>4</v>
       </c>
       <c r="G38" t="n">
-        <v>19.05</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="39">
@@ -1647,25 +1648,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>华为北京京投小站</t>
+          <t>APR成都东安天街</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F39" t="n">
         <v>4</v>
       </c>
       <c r="G39" t="n">
-        <v>66.67</v>
+        <v>44.44</v>
       </c>
     </row>
     <row r="40">
@@ -1674,25 +1675,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>APR成都东安天街</t>
+          <t>DJI北京龙湖熙悦天街授权体验店</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E40" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G40" t="n">
-        <v>44.44</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="41">
@@ -1701,25 +1702,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>华为北京通州乐堤港</t>
+          <t>APR北京大峡谷凯德茂</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F41" t="n">
         <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="42">
@@ -1728,25 +1729,25 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DJI北京龙湖熙悦天街授权体验店</t>
+          <t>华为北京房山万科</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E42" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F42" t="n">
         <v>3</v>
       </c>
       <c r="G42" t="n">
-        <v>8.33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43">
@@ -1755,25 +1756,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>APR北京大峡谷凯德茂</t>
+          <t>DJI北京望京凯德MALL授权体验店</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E43" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F43" t="n">
         <v>3</v>
       </c>
       <c r="G43" t="n">
-        <v>23.08</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="44">
@@ -1782,7 +1783,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>华为北京房山万科</t>
+          <t>华为北京来福士</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1791,16 +1792,16 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E44" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F44" t="n">
         <v>3</v>
       </c>
       <c r="G44" t="n">
-        <v>14.29</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="45">
@@ -1809,25 +1810,25 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DJI北京望京凯德MALL授权体验店</t>
+          <t>APR北京顺义华联</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="E45" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="F45" t="n">
         <v>3</v>
       </c>
       <c r="G45" t="n">
-        <v>15.79</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="46">
@@ -1836,25 +1837,25 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>华为北京来福士</t>
+          <t>DJI上海中庚漫游城授权体验店</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E46" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F46" t="n">
         <v>3</v>
       </c>
       <c r="G46" t="n">
-        <v>13.04</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="47">
@@ -1863,25 +1864,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>APR北京顺义华联</t>
+          <t>DJI上海第一八佰伴授权体验店</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="E47" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="F47" t="n">
         <v>3</v>
       </c>
       <c r="G47" t="n">
-        <v>6.52</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="48">
@@ -1890,25 +1891,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DJI上海中庚漫游城授权体验店</t>
+          <t>DJI北京翠微百货授权体验店</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E48" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F48" t="n">
         <v>3</v>
       </c>
       <c r="G48" t="n">
-        <v>8.82</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="49">
@@ -1917,25 +1918,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DJI上海第一八佰伴授权体验店</t>
+          <t>DJI北京颐堤港授权体验店</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E49" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49" t="n">
-        <v>10.34</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="50">
@@ -1944,25 +1945,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>华为北京回龙观华联</t>
+          <t>华为厦门思明罗宾森广场</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>17.65</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
@@ -1971,7 +1972,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DJI北京翠微百货授权体验店</t>
+          <t>DJI北京龙湖大兴天街授权体验店</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1980,16 +1981,16 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E51" t="n">
         <v>15</v>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G51" t="n">
-        <v>16.67</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="52">
@@ -1998,25 +1999,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>华为福州东街口</t>
+          <t>APR成都天府环宇坊</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E52" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F52" t="n">
         <v>2</v>
       </c>
       <c r="G52" t="n">
-        <v>10.53</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="53">
@@ -2025,25 +2026,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DJI北京颐堤港授权体验店</t>
+          <t>华为福州大洋晶典</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E53" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F53" t="n">
         <v>2</v>
       </c>
       <c r="G53" t="n">
-        <v>5.88</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="54">
@@ -2052,25 +2053,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>华为厦门思明罗宾森广场</t>
+          <t>APR成都三利爱琴海</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E54" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F54" t="n">
         <v>2</v>
       </c>
       <c r="G54" t="n">
-        <v>9.52</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="55">
@@ -2079,7 +2080,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DJI北京龙湖大兴天街授权体验店</t>
+          <t>DJI北京西红门荟聚中心授权体验店</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2088,16 +2089,16 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="E55" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="F55" t="n">
         <v>2</v>
       </c>
       <c r="G55" t="n">
-        <v>11.76</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="56">
@@ -2106,7 +2107,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>APR成都天府环宇坊</t>
+          <t>APR成都武侯大悦城</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2115,16 +2116,16 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F56" t="n">
         <v>2</v>
       </c>
       <c r="G56" t="n">
-        <v>18.18</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="57">
@@ -2133,25 +2134,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>华为福州大洋晶典</t>
+          <t>华为北京东坝万达</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="E57" t="n">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="F57" t="n">
         <v>2</v>
       </c>
       <c r="G57" t="n">
-        <v>14.29</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="58">
@@ -2160,25 +2161,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>APR成都三利爱琴海</t>
+          <t>DJI北京昌平悦荟授权体验店</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E58" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F58" t="n">
         <v>2</v>
       </c>
       <c r="G58" t="n">
-        <v>8.33</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="59">
@@ -2187,7 +2188,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DJI北京西红门荟聚中心授权体验店</t>
+          <t>DJI北京通州万达授权体验店</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2196,16 +2197,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="E59" t="n">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="F59" t="n">
         <v>2</v>
       </c>
       <c r="G59" t="n">
-        <v>2.94</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="60">
@@ -2214,25 +2215,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>APR成都武侯大悦城</t>
+          <t>DJI北京顺义华联授权体验店</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E60" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F60" t="n">
         <v>2</v>
       </c>
       <c r="G60" t="n">
-        <v>7.14</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="61">
@@ -2241,25 +2242,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>华为北京东坝万达</t>
+          <t>DJI北京龙湖亦庄天街授权体验店</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="E61" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="F61" t="n">
         <v>2</v>
       </c>
       <c r="G61" t="n">
-        <v>3.64</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="62">
@@ -2268,25 +2269,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DJI北京昌平悦荟授权体验店</t>
+          <t>DJI上海静安大悦城授权体验店</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E62" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F62" t="n">
         <v>2</v>
       </c>
       <c r="G62" t="n">
-        <v>6.9</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="63">
@@ -2295,25 +2296,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DJI北京通州万达授权体验店</t>
+          <t>华为南平建阳建发悦城</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E63" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F63" t="n">
         <v>2</v>
       </c>
       <c r="G63" t="n">
-        <v>5.71</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="64">
@@ -2322,7 +2323,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DJI北京顺义华联授权体验店</t>
+          <t>DJI北京丰科万达广场授权体验店</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2349,25 +2350,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DJI北京龙湖亦庄天街授权体验店</t>
+          <t>APR成都天府大悦城</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="E65" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F65" t="n">
         <v>2</v>
       </c>
       <c r="G65" t="n">
-        <v>6.9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66">
@@ -2376,25 +2377,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DJI上海静安大悦城授权体验店</t>
+          <t>华为北京昌平政府街</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E66" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F66" t="n">
         <v>2</v>
       </c>
       <c r="G66" t="n">
-        <v>7.41</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="67">
@@ -2403,25 +2404,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>华为南平建阳建发悦城</t>
+          <t>华为北京槐房万达</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E67" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F67" t="n">
         <v>2</v>
       </c>
       <c r="G67" t="n">
-        <v>16.67</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="68">
@@ -2430,25 +2431,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DJI北京丰科万达广场授权体验店</t>
+          <t>华为北京沙河万达</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E68" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F68" t="n">
         <v>2</v>
       </c>
       <c r="G68" t="n">
-        <v>8.33</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="69">
@@ -2457,25 +2458,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>APR成都天府大悦城</t>
+          <t>DJI上海长风大悦城授权体验店</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E69" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F69" t="n">
         <v>2</v>
       </c>
       <c r="G69" t="n">
-        <v>20</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="70">
@@ -2484,25 +2485,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>华为北京槐房万达</t>
+          <t>DJI上海漕河泾印象城授权体验店</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E70" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F70" t="n">
         <v>2</v>
       </c>
       <c r="G70" t="n">
-        <v>7.14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="71">
@@ -2511,25 +2512,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>华为北京沙河万达</t>
+          <t>DJI上海百联又一城授权体验店</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E71" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>12.5</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="72">
@@ -2538,25 +2539,25 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DJI上海长风大悦城授权体验店</t>
+          <t>APR北京合生汇</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="E72" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="F72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>28.57</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="73">
@@ -2565,25 +2566,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DJI上海漕河泾印象城授权体验店</t>
+          <t>APR北京五棵松华熙</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>25</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="74">
@@ -2592,25 +2593,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DJI上海百联又一城授权体验店</t>
+          <t>华为厦门思明加州广场</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E74" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F74" t="n">
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>4.55</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="75">
@@ -2619,25 +2620,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>APR北京合生汇</t>
+          <t>华为北京门头沟长安天街</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="E75" t="n">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="F75" t="n">
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>1.43</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="76">
@@ -2646,25 +2647,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>华为厦门思明宝龙一城</t>
+          <t>华为北京丰台银泰</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E76" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F76" t="n">
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>3.03</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="77">
@@ -2673,25 +2674,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>APR北京五棵松华熙</t>
+          <t>华为福州东街口</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="E77" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F77" t="n">
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>2.38</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="78">
@@ -2700,25 +2701,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>华为厦门思明加州广场</t>
+          <t>DJI大疆哈苏北京芳草地概念店</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E78" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>5.56</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="79">
@@ -2727,25 +2728,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>华为北京门头沟长安天街</t>
+          <t>APR成都金牛凯德</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E79" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F79" t="n">
         <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>4.17</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="80">
@@ -2754,25 +2755,25 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>华为北京丰台银泰</t>
+          <t>华为南平武夷山宝龙广场</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E80" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F80" t="n">
         <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>4.55</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="81">
@@ -2781,25 +2782,25 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京芳草地概念店</t>
+          <t>DJI上海维璟印象城授权体验店</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E81" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>7.69</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
@@ -2808,25 +2809,25 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>APR成都金牛凯德</t>
+          <t>华为北京亦庄龙湖</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F82" t="n">
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>5.26</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="83">
@@ -2835,25 +2836,25 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>华为南平武夷山宝龙广场</t>
+          <t>APR北京万柳华联</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E83" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>11.11</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="84">
@@ -2862,25 +2863,25 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>华为北京牡丹园翠微</t>
+          <t>APR成都双楠伊藤</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="E84" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>3.57</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="85">
@@ -2889,25 +2890,25 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DJI上海维璟印象城授权体验店</t>
+          <t>APR北京五道口购物中心</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E85" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="F85" t="n">
         <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>4</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="86">
@@ -2916,7 +2917,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>华为北京亦庄龙湖</t>
+          <t>华为北京回龙观华联</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2925,16 +2926,16 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="E86" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="F86" t="n">
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>2.13</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="87">
@@ -2943,25 +2944,25 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>APR北京万柳华联</t>
+          <t>华为福州砂之船奥莱</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F87" t="n">
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>9.09</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="88">
@@ -2970,25 +2971,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>APR成都双楠伊藤</t>
+          <t>DJI上海世博天地授权体验店</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E88" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>14.29</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="89">
@@ -2997,25 +2998,25 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>华为福州仓山爱琴海合作店</t>
+          <t>APR成都北城天街</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E89" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>14.29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90">
@@ -3024,25 +3025,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>华为北京大兴大族</t>
+          <t>华为福州中骏世界城</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E90" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -3051,25 +3052,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>APR北京五道口购物中心</t>
+          <t>华为北京通州乐堤港</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -3078,25 +3079,25 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>华为福州砂之船奥莱</t>
+          <t>APR北京怀柔万达</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E92" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>11.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -3105,25 +3106,25 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DJI上海世博天地授权体验店</t>
+          <t>DJI北京东坝万达广场授权体验店</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E93" t="n">
         <v>11</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -3132,25 +3133,25 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>APR成都北城天街</t>
+          <t>APR北京房山龙湖</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="E94" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -3159,7 +3160,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>华为福州中骏世界城</t>
+          <t>华为厦门思明宝龙一城</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3168,10 +3169,10 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E95" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -3186,19 +3187,19 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>APR北京怀柔万达</t>
+          <t>DJI上海江桥万达授权体验店</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E96" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -3213,19 +3214,19 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DJI北京东坝万达广场授权体验店</t>
+          <t>华为北京长楹龙湖</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="E97" t="n">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -3240,7 +3241,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>华为北京平谷万达</t>
+          <t>华为北京石景山万达</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3249,10 +3250,10 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E98" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -3267,19 +3268,19 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>APR北京房山龙湖</t>
+          <t>华为厦门思明瑞景广场</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="E99" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -3294,19 +3295,19 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>DJI上海江桥万达授权体验店</t>
+          <t>APR北京龙德广场</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E100" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -3321,19 +3322,19 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>华为北京长楹龙湖</t>
+          <t>APR北京旧宫万科</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="E101" t="n">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
@@ -3348,7 +3349,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>华为北京石景山万达</t>
+          <t>华为北京旧宫万科</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3357,10 +3358,10 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E102" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
@@ -3375,19 +3376,19 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>华为厦门思明瑞景广场</t>
+          <t>APR成都蜀新天街</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E103" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
@@ -3402,19 +3403,19 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>APR北京龙德广场</t>
+          <t>DJI北京西北旺万象汇授权体验店</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E104" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
@@ -3429,19 +3430,19 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>APR北京旧宫万科</t>
+          <t>华为北京首开万象汇</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="E105" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
@@ -3456,7 +3457,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>华为北京旧宫万科</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3465,10 +3466,10 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="E106" t="n">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
@@ -3483,19 +3484,19 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>APR成都蜀新天街</t>
+          <t>华为北京清河万象汇</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="E107" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F107" t="n">
         <v>0</v>
@@ -3510,19 +3511,19 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DJI北京西北旺万象汇授权体验店</t>
+          <t>华为福州五四北泰禾广场</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E108" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
@@ -3537,19 +3538,19 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>华为北京首开万象汇</t>
+          <t>DJI上海长泰广场授权体验店</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E109" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
@@ -3564,7 +3565,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京酒仙桥颐堤港</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3573,10 +3574,10 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="E110" t="n">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
@@ -3591,7 +3592,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>华为北京清河万象汇</t>
+          <t>华为北京丽泽龙湖</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3600,10 +3601,10 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="E111" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
@@ -3618,7 +3619,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>华为福州五四北泰禾广场</t>
+          <t>华为泉州石狮泰禾广场</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3627,10 +3628,10 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E112" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
@@ -3645,19 +3646,19 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>DJI上海长泰广场授权体验店</t>
+          <t>APR北京颐堤港</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E113" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
@@ -3672,19 +3673,19 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>华为北京酒仙桥颐堤港</t>
+          <t>APR北京东坝万达</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E114" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
@@ -3699,19 +3700,19 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>华为北京丽泽龙湖</t>
+          <t>APR北京亦庄龙湖</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E115" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
@@ -3726,19 +3727,19 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>华为泉州石狮泰禾广场</t>
+          <t>APR北京北苑龙湖</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E116" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F116" t="n">
         <v>0</v>
@@ -3753,19 +3754,19 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>APR北京颐堤港</t>
+          <t>华为北京丰科万达</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="E117" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
@@ -3780,7 +3781,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>APR北京东坝万达</t>
+          <t>APR北京石景山喜隆多</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3789,10 +3790,10 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E118" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
@@ -3807,7 +3808,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>APR北京亦庄龙湖</t>
+          <t>APR北京通州万达</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3816,10 +3817,10 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E119" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
@@ -3834,19 +3835,19 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>APR北京北苑龙湖</t>
+          <t>华为北京西铁营万达</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E120" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
@@ -3861,19 +3862,19 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>华为北京丰科万达</t>
+          <t>华为福州平潭吾悦</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="E121" t="n">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
@@ -3888,19 +3889,19 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>APR北京石景山喜隆多</t>
+          <t>APR成都温江旭辉</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E122" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
@@ -3915,12 +3916,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>APR北京通州万达</t>
+          <t>华为北京牡丹园翠微</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -3942,7 +3943,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>华为北京西铁营万达</t>
+          <t>华为北京北苑龙湖</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3951,10 +3952,10 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E124" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
@@ -3969,19 +3970,19 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>华为福州平潭吾悦</t>
+          <t>DJI北京京西大悦城授权体验店</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="E125" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F125" t="n">
         <v>0</v>
@@ -3996,19 +3997,19 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>APR成都温江旭辉</t>
+          <t>DJI北京龙湖长安天街授权体验店</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E126" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F126" t="n">
         <v>0</v>
@@ -4023,19 +4024,19 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>华为北京北苑龙湖</t>
+          <t>APR北京望京凯德茂</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E127" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
@@ -4050,7 +4051,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>DJI北京京西大悦城授权体验店</t>
+          <t>DJI北京昌平超级合生汇授权体验店</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4059,10 +4060,10 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E128" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
@@ -4077,19 +4078,19 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>DJI北京龙湖长安天街授权体验店</t>
+          <t>APR北京回龙观华联</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="E129" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
@@ -4104,19 +4105,19 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>APR北京望京凯德茂</t>
+          <t>华为福州仓山爱琴海</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E130" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F130" t="n">
         <v>0</v>
@@ -4131,19 +4132,19 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DJI北京昌平超级合生汇授权体验店</t>
+          <t>华为北京丰台鑫嘉汇</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E131" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F131" t="n">
         <v>0</v>
@@ -4158,7 +4159,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>APR北京回龙观华联</t>
+          <t>APR北京长安龙湖</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4167,10 +4168,10 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E132" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
@@ -4185,19 +4186,19 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>华为福州仓山爱琴海</t>
+          <t>APR北京大兴龙湖</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E133" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
@@ -4212,19 +4213,19 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>华为北京丰台鑫嘉汇</t>
+          <t>APR北京牡丹园翠微</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E134" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F134" t="n">
         <v>0</v>
@@ -4239,7 +4240,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>APR北京长安龙湖</t>
+          <t>APR北京石景山万达</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4248,10 +4249,10 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E135" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F135" t="n">
         <v>0</v>
@@ -4266,19 +4267,19 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>APR北京大兴龙湖</t>
+          <t>DJI北京龙德广场授权体验店</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E136" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F136" t="n">
         <v>0</v>
@@ -4293,7 +4294,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>APR北京牡丹园翠微</t>
+          <t>APR北京房山熙悦</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4302,10 +4303,10 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E137" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -4320,19 +4321,19 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>APR北京石景山万达</t>
+          <t>华为福州仓山爱琴海合作店</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E138" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="F138" t="n">
         <v>0</v>
@@ -4347,19 +4348,19 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>DJI北京龙德广场授权体验店</t>
+          <t>APR北京望京华彩</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E139" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -4374,19 +4375,19 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>APR北京房山熙悦</t>
+          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E140" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -4401,7 +4402,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>APR北京望京华彩</t>
+          <t>APR北京延庆万达</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4410,10 +4411,10 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E141" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -4428,19 +4429,19 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
+          <t>华为北京东坝金隅</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E142" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
@@ -4455,7 +4456,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>APR北京延庆万达</t>
+          <t>APR北京新辰汇</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4464,10 +4465,10 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E143" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F143" t="n">
         <v>0</v>
@@ -4482,7 +4483,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>华为北京东坝金隅</t>
+          <t>华为北京大兴大族</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4491,10 +4492,10 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E144" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F144" t="n">
         <v>0</v>
@@ -4509,19 +4510,19 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>APR北京新辰汇</t>
+          <t>华为北京方庄新城</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E145" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F145" t="n">
         <v>0</v>
@@ -4536,19 +4537,19 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>华为北京方庄新城</t>
+          <t>APR北京常营龙湖</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E146" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F146" t="n">
         <v>0</v>
@@ -4563,7 +4564,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>APR北京常营龙湖</t>
+          <t>APR北京大族广场</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4572,10 +4573,10 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E147" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F147" t="n">
         <v>0</v>
@@ -4590,19 +4591,19 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>APR北京大族广场</t>
+          <t>华为北京汇琴广场</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E148" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F148" t="n">
         <v>0</v>
@@ -4617,19 +4618,19 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>华为北京汇琴广场</t>
+          <t>APR北京海淀大悦城</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E149" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F149" t="n">
         <v>0</v>
@@ -4644,7 +4645,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>APR北京海淀大悦城</t>
+          <t>APR北京槐房万达</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4653,10 +4654,10 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E150" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F150" t="n">
         <v>0</v>
@@ -4671,19 +4672,19 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>APR北京槐房万达</t>
+          <t>DJI上海百联南桥购物中心授权体验店</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E151" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F151" t="n">
         <v>0</v>
@@ -4698,7 +4699,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>DJI上海百联南桥购物中心授权体验店</t>
+          <t>DJI上海虹口凯德授权体验店</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4725,19 +4726,19 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>DJI上海虹口凯德授权体验店</t>
+          <t>APR北京西三旗万象汇</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E153" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F153" t="n">
         <v>0</v>
@@ -4752,19 +4753,19 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>APR北京西三旗万象汇</t>
+          <t>APR成都龙泉吾悦</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="E154" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
@@ -4779,19 +4780,19 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>APR成都龙泉吾悦</t>
+          <t>华为北京回龙观万科</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E155" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F155" t="n">
         <v>0</v>
@@ -4806,19 +4807,19 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>华为北京同成街华联</t>
+          <t>APR北京西铁营万达</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E156" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F156" t="n">
         <v>0</v>
@@ -4833,19 +4834,19 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>华为北京回龙观万科</t>
+          <t>APR北京大红门银泰</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E157" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F157" t="n">
         <v>0</v>
@@ -4860,19 +4861,19 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>APR北京西铁营万达</t>
+          <t>华为北京平谷万达</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E158" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F158" t="n">
         <v>0</v>
@@ -4887,12 +4888,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>APR北京大红门银泰</t>
+          <t>华为北京上德银泰</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -4914,19 +4915,19 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>华为北京上德银泰</t>
+          <t>APR北京丽泽龙湖</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E160" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F160" t="n">
         <v>0</v>
@@ -4941,19 +4942,19 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>APR北京丽泽龙湖</t>
+          <t>华为厦门湖里蔡塘爱琴海</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E161" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
@@ -4968,12 +4969,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>华为厦门湖里蔡塘爱琴海</t>
+          <t>APR北京昌发展万科</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -4995,12 +4996,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>APR北京昌发展万科</t>
+          <t>华为北京房山燕隆汇</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -5022,7 +5023,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>华为北京房山燕隆汇</t>
+          <t>华为北京同成街华联</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5031,10 +5032,10 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E164" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F164" t="n">
         <v>0</v>
@@ -5270,7 +5271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5307,14 +5308,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="C2" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>各分公司门店数：上海爱飞 13家、北京中恒 4家、北京易联 12家、北京飞航 31家、四川新跃 17家、福建易联 9家</t>
+          <t>各分公司门店数：上海爱飞 13家、北京中恒 4家、北京易联 10家、北京飞航 31家、四川新跃 17家、福建易联 7家</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5326,7 +5327,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>130****7661</t>
+          <t>135****5980</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5337,19 +5338,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>APR成都科华王府井</t>
+          <t>DJI北京蓝色港湾授权体验店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>135****5980</t>
+          <t>130****7661</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5360,19 +5361,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DJI北京蓝色港湾授权体验店</t>
+          <t>APR成都科华王府井</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>177****6608</t>
+          <t>159****4633</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5383,19 +5384,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>华为北京延庆万达</t>
+          <t>APR成都科华王府井</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>159****4633</t>
+          <t>177****6608</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5406,12 +5407,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>APR成都科华王府井</t>
+          <t>华为北京延庆万达</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
@@ -5464,7 +5465,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>188****7964</t>
+          <t>135****0175</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5475,7 +5476,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>APR北京大峡谷凯德茂</t>
+          <t>APR北京顺义华联</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5487,7 +5488,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>136****5338</t>
+          <t>177****0077</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5498,19 +5499,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DJI北京朝阳大悦城授权体验店</t>
+          <t>华为北京来福士</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>138****3402</t>
+          <t>138****6407</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5521,7 +5522,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DJI上海美罗城授权体验店</t>
+          <t>DJI上海中庚漫游城授权体验店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5556,7 +5557,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>156****8363</t>
+          <t>135****5494</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5567,19 +5568,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京朝阳合生汇概念店</t>
+          <t>DJI上海复地活力城授权体验店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>136****3123</t>
+          <t>137****7690</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5590,7 +5591,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DJI北京中关村大融城授权体验店</t>
+          <t>DJI北京万柳华联授权体验店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5602,7 +5603,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>138****6407</t>
+          <t>136****3123</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5613,19 +5614,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DJI上海中庚漫游城授权体验店</t>
+          <t>DJI北京中关村大融城授权体验店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>135****5494</t>
+          <t>136****5338</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5636,19 +5637,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DJI上海复地活力城授权体验店</t>
+          <t>DJI北京朝阳大悦城授权体验店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>195****9249</t>
+          <t>139****3525</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5659,19 +5660,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DJI上海长宁龙之梦授权体验店</t>
+          <t>APR成都西宸天街</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>四川新跃</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>137****7690</t>
+          <t>138****3402</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -5682,19 +5683,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DJI北京万柳华联授权体验店</t>
+          <t>DJI上海美罗城授权体验店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>135****0175</t>
+          <t>195****9249</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -5705,19 +5706,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>APR北京顺义华联</t>
+          <t>DJI上海长宁龙之梦授权体验店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>上海爱飞</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>139****3525</t>
+          <t>136****4463</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -5728,19 +5729,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>APR成都西宸天街</t>
+          <t>华为北京延庆万达</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>177****0077</t>
+          <t>188****7964</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -5751,19 +5752,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>华为北京来福士</t>
+          <t>APR北京大峡谷凯德茂</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>136****4463</t>
+          <t>156****8363</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -5774,35 +5775,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>华为北京延庆万达</t>
+          <t>DJI大疆哈苏北京朝阳合生汇概念店</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>北京易联</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>135****8776</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>3</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>华为北京通州乐堤港</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5875,7 +5853,7 @@
         <v>17</v>
       </c>
       <c r="F2" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="3">
@@ -5894,7 +5872,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>135****5632</t>
+          <t>137****7690</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -5920,7 +5898,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>137****7690</t>
+          <t>135****5632</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -5953,7 +5931,7 @@
         <v>22</v>
       </c>
       <c r="F5" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="6">
@@ -5979,7 +5957,7 @@
         <v>22</v>
       </c>
       <c r="F6" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="7">
@@ -6005,7 +5983,7 @@
         <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8">
@@ -6031,7 +6009,7 @@
         <v>18</v>
       </c>
       <c r="F8" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9">
@@ -6057,7 +6035,7 @@
         <v>13</v>
       </c>
       <c r="F9" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="10">
@@ -6109,7 +6087,7 @@
         <v>17</v>
       </c>
       <c r="F11" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12">
@@ -6135,7 +6113,7 @@
         <v>12</v>
       </c>
       <c r="F12" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="13">
@@ -6187,7 +6165,7 @@
         <v>14</v>
       </c>
       <c r="F14" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="15">
@@ -6213,7 +6191,7 @@
         <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="16">
@@ -6239,7 +6217,7 @@
         <v>13</v>
       </c>
       <c r="F16" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="17">
@@ -6265,7 +6243,7 @@
         <v>13</v>
       </c>
       <c r="F17" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="18">
@@ -6291,7 +6269,7 @@
         <v>9</v>
       </c>
       <c r="F18" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="19">
@@ -6395,7 +6373,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="23">
@@ -6421,7 +6399,7 @@
         <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="24">
@@ -6473,7 +6451,7 @@
         <v>9</v>
       </c>
       <c r="F25" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="26">
@@ -6499,7 +6477,7 @@
         <v>9</v>
       </c>
       <c r="F26" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="27">
@@ -6525,7 +6503,7 @@
         <v>9</v>
       </c>
       <c r="F27" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="28">
@@ -6551,7 +6529,7 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="29">
@@ -6577,7 +6555,7 @@
         <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="30">
@@ -6603,7 +6581,7 @@
         <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="31">
@@ -6655,7 +6633,7 @@
         <v>7</v>
       </c>
       <c r="F32" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="33">
@@ -6726,14 +6704,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>136****3123</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E35" t="n">
         <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>396</v>
       </c>
     </row>
     <row r="36">
@@ -6752,14 +6730,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>136****3123</t>
         </is>
       </c>
       <c r="E36" t="n">
         <v>3</v>
       </c>
       <c r="F36" t="n">
-        <v>407</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -6785,18 +6763,18 @@
         <v>6</v>
       </c>
       <c r="F37" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>华为北京昌平政府街</t>
+          <t>APR成都凯德魅力城</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -6811,13 +6789,13 @@
         <v>6</v>
       </c>
       <c r="F38" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>APR成都凯德魅力城</t>
+          <t>APR成都高新伊藤</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6826,7 +6804,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6834,21 +6812,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F39" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>APR成都高新伊藤</t>
+          <t>DJI北京朝阳大悦城授权体验店</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -6856,14 +6834,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>136****5338</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>407</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -6882,25 +6860,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>136****5338</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>396</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DJI北京朝阳大悦城授权体验店</t>
+          <t>APR成都金楠天街</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -6912,16 +6890,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F42" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>APR成都金楠天街</t>
+          <t>APR成都温江伊藤</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6930,7 +6908,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6938,21 +6916,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>APR成都温江伊藤</t>
+          <t>DJI上海静安大融城授权体验店</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -6967,18 +6945,18 @@
         <v>4</v>
       </c>
       <c r="F44" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DJI上海静安大融城授权体验店</t>
+          <t>DJI北京丽泽天街授权体验店</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -6993,18 +6971,18 @@
         <v>4</v>
       </c>
       <c r="F45" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DJI北京丽泽天街授权体验店</t>
+          <t>DJI上海凯德晶萃授权体验店</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -7019,13 +6997,13 @@
         <v>4</v>
       </c>
       <c r="F46" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DJI上海凯德晶萃授权体验店</t>
+          <t>DJI上海复地活力城授权体验店</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7038,14 +7016,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>135****5494</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F47" t="n">
-        <v>407</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -7064,25 +7042,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>135****5494</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>396</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DJI上海复地活力城授权体验店</t>
+          <t>APR成都西宸天街</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -7090,14 +7068,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>139****3525</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F49" t="n">
-        <v>407</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -7116,25 +7094,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>139****3525</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>3</v>
+        <v>396</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>APR成都西宸天街</t>
+          <t>DJI北京太阳宫凯德授权体验店</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -7146,21 +7124,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F51" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DJI北京太阳宫凯德授权体验店</t>
+          <t>华为北京京投小站</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -7168,25 +7146,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>131****2308</t>
         </is>
       </c>
       <c r="E52" t="n">
         <v>4</v>
       </c>
       <c r="F52" t="n">
-        <v>407</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>华为北京京投小站</t>
+          <t>APR成都东安天街</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -7194,29 +7172,29 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>131****2308</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E53" t="n">
         <v>4</v>
       </c>
       <c r="F53" t="n">
-        <v>4</v>
+        <v>396</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>APR成都东安天街</t>
+          <t>DJI北京龙湖熙悦天街授权体验店</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7224,21 +7202,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F54" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>华为北京通州乐堤港</t>
+          <t>APR北京大峡谷凯德茂</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -7246,7 +7224,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>135****8776</t>
+          <t>188****7964</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -7259,12 +7237,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DJI北京龙湖熙悦天街授权体验店</t>
+          <t>华为北京房山万科</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -7279,18 +7257,18 @@
         <v>3</v>
       </c>
       <c r="F56" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>APR北京大峡谷凯德茂</t>
+          <t>DJI北京望京凯德MALL授权体验店</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -7298,20 +7276,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>188****7964</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E57" t="n">
         <v>3</v>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>396</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>华为北京房山万科</t>
+          <t>华为北京来福士</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7324,25 +7302,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>177****0077</t>
         </is>
       </c>
       <c r="E58" t="n">
         <v>3</v>
       </c>
       <c r="F58" t="n">
-        <v>407</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DJI北京望京凯德MALL授权体验店</t>
+          <t>APR北京顺义华联</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -7350,25 +7328,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>135****0175</t>
         </is>
       </c>
       <c r="E59" t="n">
         <v>3</v>
       </c>
       <c r="F59" t="n">
-        <v>407</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>华为北京来福士</t>
+          <t>DJI上海中庚漫游城授权体验店</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -7376,7 +7354,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>177****0077</t>
+          <t>138****6407</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -7389,12 +7367,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>APR北京顺义华联</t>
+          <t>DJI上海第一八佰伴授权体验店</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -7402,25 +7380,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>135****0175</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E61" t="n">
         <v>3</v>
       </c>
       <c r="F61" t="n">
-        <v>3</v>
+        <v>396</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DJI上海中庚漫游城授权体验店</t>
+          <t>DJI北京翠微百货授权体验店</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7428,29 +7406,29 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>138****6407</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E62" t="n">
         <v>3</v>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>396</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DJI上海第一八佰伴授权体验店</t>
+          <t>DJI北京颐堤港授权体验店</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7458,25 +7436,25 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F63" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>华为北京回龙观华联</t>
+          <t>华为厦门思明罗宾森广场</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7484,16 +7462,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DJI北京翠微百货授权体验店</t>
+          <t>DJI北京龙湖大兴天街授权体验店</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7502,7 +7480,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7510,21 +7488,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>华为福州东街口</t>
+          <t>APR成都天府环宇坊</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -7539,18 +7517,18 @@
         <v>2</v>
       </c>
       <c r="F66" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DJI北京颐堤港授权体验店</t>
+          <t>华为福州大洋晶典</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -7565,18 +7543,18 @@
         <v>2</v>
       </c>
       <c r="F67" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>华为厦门思明罗宾森广场</t>
+          <t>APR成都三利爱琴海</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -7591,13 +7569,13 @@
         <v>2</v>
       </c>
       <c r="F68" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DJI北京龙湖大兴天街授权体验店</t>
+          <t>DJI北京西红门荟聚中心授权体验店</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7617,13 +7595,13 @@
         <v>2</v>
       </c>
       <c r="F69" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>APR成都天府环宇坊</t>
+          <t>APR成都武侯大悦城</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7643,18 +7621,18 @@
         <v>2</v>
       </c>
       <c r="F70" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>华为福州大洋晶典</t>
+          <t>华为北京东坝万达</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -7669,18 +7647,18 @@
         <v>2</v>
       </c>
       <c r="F71" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>APR成都三利爱琴海</t>
+          <t>DJI北京昌平悦荟授权体验店</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -7695,13 +7673,13 @@
         <v>2</v>
       </c>
       <c r="F72" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DJI北京西红门荟聚中心授权体验店</t>
+          <t>DJI北京通州万达授权体验店</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7721,18 +7699,18 @@
         <v>2</v>
       </c>
       <c r="F73" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>APR成都武侯大悦城</t>
+          <t>DJI北京顺义华联授权体验店</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -7747,18 +7725,18 @@
         <v>2</v>
       </c>
       <c r="F74" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>华为北京东坝万达</t>
+          <t>DJI北京龙湖亦庄天街授权体验店</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -7773,18 +7751,18 @@
         <v>2</v>
       </c>
       <c r="F75" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DJI北京昌平悦荟授权体验店</t>
+          <t>DJI上海静安大悦城授权体验店</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -7799,18 +7777,18 @@
         <v>2</v>
       </c>
       <c r="F76" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DJI北京通州万达授权体验店</t>
+          <t>华为南平建阳建发悦城</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -7825,13 +7803,13 @@
         <v>2</v>
       </c>
       <c r="F77" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DJI北京顺义华联授权体验店</t>
+          <t>DJI北京丰科万达广场授权体验店</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7851,18 +7829,18 @@
         <v>2</v>
       </c>
       <c r="F78" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DJI北京龙湖亦庄天街授权体验店</t>
+          <t>APR成都天府大悦城</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -7877,18 +7855,18 @@
         <v>2</v>
       </c>
       <c r="F79" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DJI上海静安大悦城授权体验店</t>
+          <t>华为北京昌平政府街</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -7903,18 +7881,18 @@
         <v>2</v>
       </c>
       <c r="F80" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>华为南平建阳建发悦城</t>
+          <t>华为北京槐房万达</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -7929,18 +7907,18 @@
         <v>2</v>
       </c>
       <c r="F81" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DJI北京丰科万达广场授权体验店</t>
+          <t>华为北京沙河万达</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -7955,18 +7933,18 @@
         <v>2</v>
       </c>
       <c r="F82" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>APR成都天府大悦城</t>
+          <t>DJI上海长风大悦城授权体验店</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -7981,18 +7959,18 @@
         <v>2</v>
       </c>
       <c r="F83" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>华为北京槐房万达</t>
+          <t>DJI上海漕河泾印象城授权体验店</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -8007,22 +7985,22 @@
         <v>2</v>
       </c>
       <c r="F84" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>华为北京沙河万达</t>
+          <t>DJI上海百联又一城授权体验店</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8030,25 +8008,25 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DJI上海长风大悦城授权体验店</t>
+          <t>APR北京合生汇</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8056,25 +8034,25 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F86" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DJI上海漕河泾印象城授权体验店</t>
+          <t>APR北京五棵松华熙</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8082,21 +8060,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DJI上海百联又一城授权体验店</t>
+          <t>华为厦门思明加州广场</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -8111,18 +8089,18 @@
         <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>APR北京合生汇</t>
+          <t>华为北京门头沟长安天街</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -8137,18 +8115,18 @@
         <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>华为厦门思明宝龙一城</t>
+          <t>华为北京丰台银泰</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -8163,18 +8141,18 @@
         <v>1</v>
       </c>
       <c r="F90" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>APR北京五棵松华熙</t>
+          <t>华为福州东街口</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -8189,18 +8167,18 @@
         <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>华为厦门思明加州广场</t>
+          <t>DJI大疆哈苏北京芳草地概念店</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -8215,18 +8193,18 @@
         <v>1</v>
       </c>
       <c r="F92" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>华为北京门头沟长安天街</t>
+          <t>APR成都金牛凯德</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -8241,18 +8219,18 @@
         <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>华为北京丰台银泰</t>
+          <t>华为南平武夷山宝龙广场</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -8267,18 +8245,18 @@
         <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京芳草地概念店</t>
+          <t>DJI上海维璟印象城授权体验店</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -8293,18 +8271,18 @@
         <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>APR成都金牛凯德</t>
+          <t>华为北京亦庄龙湖</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -8319,18 +8297,18 @@
         <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>华为南平武夷山宝龙广场</t>
+          <t>APR北京万柳华联</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -8345,18 +8323,18 @@
         <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>华为北京牡丹园翠微</t>
+          <t>APR成都双楠伊藤</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -8371,18 +8349,18 @@
         <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DJI上海维璟印象城授权体验店</t>
+          <t>APR北京五道口购物中心</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -8397,13 +8375,13 @@
         <v>1</v>
       </c>
       <c r="F99" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>华为北京亦庄龙湖</t>
+          <t>华为北京回龙观华联</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8423,18 +8401,18 @@
         <v>1</v>
       </c>
       <c r="F100" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>APR北京万柳华联</t>
+          <t>华为福州砂之船奥莱</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -8449,18 +8427,18 @@
         <v>1</v>
       </c>
       <c r="F101" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>APR成都双楠伊藤</t>
+          <t>DJI上海世博天地授权体验店</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -8475,18 +8453,18 @@
         <v>1</v>
       </c>
       <c r="F102" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>华为福州仓山爱琴海合作店</t>
+          <t>APR成都北城天街</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -8501,137 +8479,7 @@
         <v>1</v>
       </c>
       <c r="F103" t="n">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>华为北京大兴大族</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>北京易联</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>1</v>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>177****3777</t>
-        </is>
-      </c>
-      <c r="E104" t="n">
-        <v>1</v>
-      </c>
-      <c r="F104" t="n">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>APR北京五道口购物中心</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>北京中恒</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>1</v>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>177****3777</t>
-        </is>
-      </c>
-      <c r="E105" t="n">
-        <v>1</v>
-      </c>
-      <c r="F105" t="n">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>华为福州砂之船奥莱</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>福建易联</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>1</v>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>177****3777</t>
-        </is>
-      </c>
-      <c r="E106" t="n">
-        <v>1</v>
-      </c>
-      <c r="F106" t="n">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>DJI上海世博天地授权体验店</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>上海爱飞</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>1</v>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>177****3777</t>
-        </is>
-      </c>
-      <c r="E107" t="n">
-        <v>1</v>
-      </c>
-      <c r="F107" t="n">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>APR成都北城天街</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>四川新跃</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>1</v>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>177****3777</t>
-        </is>
-      </c>
-      <c r="E108" t="n">
-        <v>1</v>
-      </c>
-      <c r="F108" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -8739,4 +8587,1450 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>单据日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>业务组织</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>所属分公司</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>内部业务</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>单据编号</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>单据类型</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>会员手机号</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>商品分类名称</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>商品编码</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>实收金额(合计)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>华为北京大兴大族</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>LSD2026080100896132</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>畅享 90</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6942103188220</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>7996</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>华为北京大兴大族</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>LSD2026080100896132</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>畅享 90</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6942103188213</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>7996</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>华为北京大兴大族</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>LSD2026080100896132</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>畅享 90</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>6942103188237</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>7996</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>华为北京大兴大族</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>LSD2026080100896132</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>畅享 90</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>6942103188213</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>7996</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>华为北京昌平政府街</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LSD2026080100900497</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>nova 16</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>nova 16 EMA-AL00U 256GB 幻彩贝母</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>6942103199264</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>15496</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>华为北京昌平政府街</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LSD2026080100900497</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>nova 16</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>nova 16 EMA-AL00U 512GB 天际白</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6942103199295</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>15496</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>华为北京昌平政府街</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>LSD2026080100900497</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Mate 80</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Mate 80 VYG-AL30(16GB+512GB) 晨曦金</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6942103191695</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>15496</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>华为北京昌平政府街</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LSD2026080100900497</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>nova 16</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>nova 16 EMA-AL00U 512GB 星空黑</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>6942103199271</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>15496</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>华为北京东坝金隅</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>LSD2026080200906563</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>178****1826</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>保护</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>三源 TimeLock Pura X Max 巧匠-超薄碳纳米纤维磁吸支架保护壳 橙色</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>6979434900801</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>华为北京北苑龙湖</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>LSD2026080200906317</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>+86-131****1665</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>FreeClip</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>FreeClip 2 耳夹耳机无线充 玫瑰金</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>6942103178726</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>华为北京昌平政府街</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>LSD2026080200902559</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Pura 80</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pura 80 Pro LMR-AL00 12GB+512GB 釉白</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>6942103162466</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>16497</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>华为北京昌平政府街</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>LSD2026080200902559</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Pura 80</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Pura 80 Pro LMR-AL00 12GB+512GB 釉白</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>6942103162466</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>16497</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>华为北京昌平政府街</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LSD2026080200902559</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Pura 80</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pura 80 Pro LMR-AL00 12GB+512GB 釉白</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>6942103184901</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>16497</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>华为北京昌平政府街</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LSD2026080200902568</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Pura 90</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pura 90 Pro Max SCA-AL00 12GB+512GB 曜石黑</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>6942103198274</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>6999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>华为北京昌平政府街</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LSD2026080200902738</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>畅享 90</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 雪域白</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>6942103188268</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>9196</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>华为北京昌平政府街</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>LSD2026080200902738</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>畅享 90</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>6942103188220</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>9196</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>华为北京昌平政府街</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LSD2026080200902738</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>畅享 90</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>6942103188275</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>9196</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>华为北京昌平政府街</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LSD2026080200902738</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>畅享 90</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 晨曦金</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>6942103188251</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>9196</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>华为北京牡丹园翠微</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LSD2026080200906149</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Mate 80</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Mate 80 VYG-AL00(12GB+512GB) 曜石黑</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>6942103177415</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>5199</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>华为北京门头沟长安天街</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LSD2026080200904103</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>+86-153****9909</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>nova 14</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>nova 14 Pro 12GB+512GB 羽砂黑 昆仑玻璃</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>6942103162114</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>23494</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>华为北京门头沟长安天街</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LSD2026080200904103</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>+86-153****9909</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>nova 14</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>nova 14 Pro 12GB+512GB 凝霜白 昆仑玻璃</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>6942103162121</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>23494</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>华为北京门头沟长安天街</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LSD2026080200904103</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>+86-153****9909</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>nova 14</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>nova 14 Pro 12GB+512GB 羽砂黑</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>6942103160080</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>23494</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>华为北京门头沟长安天街</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LSD2026080200904103</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>+86-153****9909</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>nova 14</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>nova 14 Ultra 12GB+256GB 曜金黑</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>6942103158711</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>23494</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>华为北京门头沟长安天街</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LSD2026080200904103</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>+86-153****9909</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>nova 14</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>nova 14 Pro 12GB+256GB 冰晶蓝</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>6942103160066</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>23494</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>华为北京门头沟长安天街</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>礼品机出库</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LSD2026080200904103</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>+86-153****9909</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>nova 14</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>nova 14 Pro 12GB+512GB 凝霜白 昆仑玻璃</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>6942103162121</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>23494</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>